--- a/Portfolio/Portfolio_Rebalancing_Template.xlsx
+++ b/Portfolio/Portfolio_Rebalancing_Template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="21795" windowHeight="12975" activeTab="2"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Price_Data" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="126">
   <si>
     <t>Ticker</t>
   </si>
@@ -227,9 +227,6 @@
   </si>
   <si>
     <t>종목 선정</t>
-  </si>
-  <si>
-    <t>6M 모멘텀</t>
   </si>
   <si>
     <t>확신도</t>
@@ -365,14 +362,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Bloomberg China Tech Select Top 10</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BCTST10T:IND</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>FRO</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -442,6 +431,22 @@
   </si>
   <si>
     <t>1. 주식 vs 채권</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>3M 수익률</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>3M 모멘텀</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0047A0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIGER 차이나테크 TOP10</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -919,92 +924,92 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>6840.2</v>
+        <v>6644.31</v>
       </c>
       <c r="D2" s="2">
-        <v>6339.39</v>
+        <v>6415.54</v>
       </c>
       <c r="E2" s="2">
-        <v>5650.38</v>
+        <v>5935.94</v>
       </c>
       <c r="F2" s="2">
-        <v>5712.69</v>
+        <v>6047.15</v>
       </c>
       <c r="G2" s="3">
         <f t="shared" ref="G2:G8" si="0">(C2-D2)/D2*100</f>
-        <v>7.89997144835701</v>
+        <v>3.5658728649498004</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" ref="H2:H8" si="1">(C2-E2)/E2*100</f>
-        <v>21.057344815746902</v>
+        <v>11.933577495729418</v>
       </c>
       <c r="I2" s="3">
         <f t="shared" ref="I2:I8" si="2">(C2-F2)/F2*100</f>
-        <v>19.736936539528667</v>
+        <v>9.8750651133178575</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2">
-        <v>579.46</v>
+        <v>554</v>
       </c>
       <c r="D3" s="2">
-        <v>438.6</v>
+        <v>423</v>
       </c>
       <c r="E3" s="2">
-        <v>341.31</v>
+        <v>360</v>
       </c>
       <c r="F3" s="2">
-        <v>341.37</v>
+        <v>325</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" si="0"/>
-        <v>32.115823073415413</v>
+        <v>30.969267139479907</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" si="1"/>
-        <v>69.775277606867675</v>
+        <v>53.888888888888886</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" si="2"/>
-        <v>69.745437501830864</v>
+        <v>70.461538461538467</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C4" s="2">
-        <v>2061.3200000000002</v>
+        <v>12770</v>
       </c>
       <c r="D4" s="2">
-        <v>1905.61</v>
+        <v>11929</v>
       </c>
       <c r="E4" s="2">
-        <v>1896.39</v>
+        <v>9275</v>
       </c>
       <c r="F4" s="2">
-        <v>1646.91</v>
+        <v>10138</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" ref="G4" si="3">(C4-D4)/D4*100</f>
-        <v>8.1711368013392178</v>
+        <v>7.0500461061279234</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4" si="4">(C4-E4)/E4*100</f>
-        <v>8.6970507121425467</v>
+        <v>37.681940700808624</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" ref="I4" si="5">(C4-F4)/F4*100</f>
-        <v>25.162880788871284</v>
+        <v>25.961728151509174</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1015,28 +1020,28 @@
         <v>13</v>
       </c>
       <c r="C5" s="2">
-        <v>90.29</v>
+        <v>90.21</v>
       </c>
       <c r="D5" s="2">
-        <v>86.92</v>
+        <v>86.28</v>
       </c>
       <c r="E5" s="2">
-        <v>87.24</v>
+        <v>83.49</v>
       </c>
       <c r="F5" s="2">
-        <v>92.25</v>
+        <v>90.33</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>3.8771283939254539</v>
+        <v>4.5549374130737048</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="1"/>
-        <v>3.4961027051811229</v>
+        <v>8.0488681279195102</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="2"/>
-        <v>-2.124661246612459</v>
+        <v>-0.13284623048821492</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1049,194 +1054,194 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2">
-        <v>25.04</v>
+        <v>23.52</v>
       </c>
       <c r="D7" s="2">
-        <v>18.93</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="E7" s="2">
-        <v>17.34</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="F7" s="2">
-        <v>18.399999999999999</v>
+        <v>15.57</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
-        <v>32.276809297411511</v>
+        <v>15.29411764705883</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="1"/>
-        <v>44.405997693194919</v>
+        <v>37.543859649122794</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="2"/>
-        <v>36.08695652173914</v>
+        <v>51.059730250481692</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2">
-        <v>30.91</v>
+        <v>36.43</v>
       </c>
       <c r="D8" s="2">
-        <v>33.020000000000003</v>
+        <v>32.14</v>
       </c>
       <c r="E8" s="2">
-        <v>35.49</v>
+        <v>38.97</v>
       </c>
       <c r="F8" s="2">
-        <v>26.57</v>
+        <v>32.69</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>-6.3900666262871066</v>
+        <v>13.347853142501553</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="1"/>
-        <v>-12.905043674274447</v>
+        <v>-6.5178342314600961</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="2"/>
-        <v>16.334211516748212</v>
+        <v>11.440807586417872</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C9" s="2">
-        <v>70.5</v>
+        <v>74.81</v>
       </c>
       <c r="D9" s="2">
-        <v>50.93</v>
+        <v>61.7</v>
       </c>
       <c r="E9" s="2">
-        <v>37.89</v>
+        <v>36.53</v>
       </c>
       <c r="F9" s="2">
-        <v>47.31</v>
+        <v>44.82</v>
       </c>
       <c r="G9" s="3">
-        <f t="shared" ref="G9:G11" si="6">(C9-D9)/D9*100</f>
-        <v>38.425289613194579</v>
+        <f>(C9-D9)/D9*100</f>
+        <v>21.247974068071311</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" ref="H9:H11" si="7">(C9-E9)/E9*100</f>
-        <v>86.064924782264455</v>
+        <f>(C9-E9)/E9*100</f>
+        <v>104.79058308239803</v>
       </c>
       <c r="I9" s="3">
-        <f t="shared" ref="I9:I11" si="8">(C9-F9)/F9*100</f>
-        <v>49.017121116043114</v>
+        <f>(C9-F9)/F9*100</f>
+        <v>66.912092815707283</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2">
-        <v>5.09</v>
+        <v>5.21</v>
       </c>
       <c r="D10" s="2">
-        <v>4.4400000000000004</v>
+        <v>4.51</v>
       </c>
       <c r="E10" s="2">
-        <v>4.6500000000000004</v>
+        <v>4.83</v>
       </c>
       <c r="F10" s="2">
-        <v>4.41</v>
+        <v>4.08</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" si="6"/>
-        <v>14.639639639639626</v>
+        <f>(C10-D10)/D10*100</f>
+        <v>15.521064301552112</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="7"/>
-        <v>9.4623655913978375</v>
+        <f>(C10-E10)/E10*100</f>
+        <v>7.8674948240165605</v>
       </c>
       <c r="I10" s="3">
-        <f t="shared" si="8"/>
-        <v>15.419501133786842</v>
+        <f>(C10-F10)/F10*100</f>
+        <v>27.696078431372545</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2">
-        <v>82.4</v>
+        <v>76.45</v>
       </c>
       <c r="D11" s="2">
-        <v>71.45</v>
+        <v>75.05</v>
       </c>
       <c r="E11" s="2">
-        <v>70.2</v>
+        <v>71.95</v>
       </c>
       <c r="F11" s="2">
-        <v>78.2</v>
+        <v>77.5</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" si="6"/>
-        <v>15.325402379286219</v>
+        <f t="shared" ref="G11" si="6">(C11-D11)/D11*100</f>
+        <v>1.8654230512991414</v>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="7"/>
-        <v>17.378917378917382</v>
+        <f t="shared" ref="H11" si="7">(C11-E11)/E11*100</f>
+        <v>6.2543432939541344</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" si="8"/>
-        <v>5.3708439897698241</v>
+        <f t="shared" ref="I11" si="8">(C11-F11)/F11*100</f>
+        <v>-1.3548387096774157</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2">
-        <v>4004.43</v>
+        <v>4255.1000000000004</v>
       </c>
       <c r="D12" s="2">
-        <v>3374.26</v>
+        <v>3476.7</v>
       </c>
       <c r="E12" s="2">
-        <v>3334.53</v>
+        <v>3381.7</v>
       </c>
       <c r="F12" s="2">
-        <v>2736</v>
+        <v>2642.21</v>
       </c>
       <c r="G12" s="3">
         <f>(C12-D12)/D12*100</f>
-        <v>18.675798545458843</v>
+        <v>22.389047084879358</v>
       </c>
       <c r="H12" s="3">
         <f>(C12-E12)/E12*100</f>
-        <v>20.089787766191925</v>
+        <v>25.827246651092661</v>
       </c>
       <c r="I12" s="3">
         <f>(C12-F12)/F12*100</f>
-        <v>46.360745614035082</v>
+        <v>61.043217609501141</v>
       </c>
     </row>
   </sheetData>
@@ -1250,7 +1255,9 @@
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="14" customWidth="1"/>
+    <col min="1" max="1" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="14" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25" x14ac:dyDescent="0.35">
@@ -1268,7 +1275,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
@@ -1294,8 +1301,8 @@
         <v>10</v>
       </c>
       <c r="B5" s="3">
-        <f>Price_Data!H2</f>
-        <v>21.057344815746902</v>
+        <f>Price_Data!G2</f>
+        <v>3.5658728649498004</v>
       </c>
       <c r="C5" t="str">
         <f>IF(B5&gt;0,"🟢","🔴")</f>
@@ -1303,15 +1310,15 @@
       </c>
       <c r="D5" s="3">
         <f>IF(B5&gt;0,B5,0)</f>
-        <v>21.057344815746902</v>
+        <v>3.5658728649498004</v>
       </c>
       <c r="E5" s="9">
         <f>(1+D5/100)^$K$4</f>
-        <v>1.4654880733838644</v>
+        <v>1.0725890022278946</v>
       </c>
       <c r="F5" s="3">
         <f>E5/SUM($E$5:$E$7)*100</f>
-        <v>26.503768075386891</v>
+        <v>27.265594842751241</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -1319,8 +1326,8 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <f>Price_Data!H3</f>
-        <v>69.775277606867675</v>
+        <f>Price_Data!G3</f>
+        <v>30.969267139479907</v>
       </c>
       <c r="C6" t="str">
         <f>IF(B6&gt;0,"🟢","🔴")</f>
@@ -1328,25 +1335,25 @@
       </c>
       <c r="D6" s="3">
         <f>IF(B6&gt;0,B6,0)</f>
-        <v>69.775277606867675</v>
+        <v>30.969267139479907</v>
       </c>
       <c r="E6" s="9">
         <f>(1+D6/100)^$K$4</f>
-        <v>2.8823644886488986</v>
+        <v>1.7152948935052448</v>
       </c>
       <c r="F6" s="3">
         <f t="shared" ref="F6:F7" si="0">E6/SUM($E$5:$E$7)*100</f>
-        <v>52.128380505674244</v>
+        <v>43.603407740532809</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>Price_Data!B4</f>
-        <v>Bloomberg China Tech Select Top 10</v>
+        <v>TIGER 차이나테크 TOP10</v>
       </c>
       <c r="B7" s="3">
-        <f>Price_Data!H4</f>
-        <v>8.6970507121425467</v>
+        <f>Price_Data!G4</f>
+        <v>7.0500461061279234</v>
       </c>
       <c r="C7" t="str">
         <f>IF(B7&gt;0,"🟢","🔴")</f>
@@ -1354,15 +1361,15 @@
       </c>
       <c r="D7" s="3">
         <f>IF(B7&gt;0,B7,0)</f>
-        <v>8.6970507121425467</v>
+        <v>7.0500461061279234</v>
       </c>
       <c r="E7" s="9">
         <f>(1+D7/100)^$K$4</f>
-        <v>1.1815048833518089</v>
+        <v>1.1459712371324113</v>
       </c>
       <c r="F7" s="3">
         <f t="shared" si="0"/>
-        <v>21.367851418938862</v>
+        <v>29.130997416715953</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -1380,7 +1387,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
@@ -1406,8 +1413,8 @@
         <v>24</v>
       </c>
       <c r="B12" s="3">
-        <f>Price_Data!H5</f>
-        <v>3.4961027051811229</v>
+        <f>Price_Data!G5</f>
+        <v>4.5549374130737048</v>
       </c>
       <c r="C12" t="str">
         <f>IF(B12&gt;0,"🟢","🔴")</f>
@@ -1415,11 +1422,11 @@
       </c>
       <c r="D12" s="3">
         <f>IF(B12&gt;0,B12,0)</f>
-        <v>3.4961027051811229</v>
+        <v>4.5549374130737048</v>
       </c>
       <c r="E12" s="9">
         <f>(1+D12/100)^$K$11</f>
-        <v>1.0528972567761898</v>
+        <v>1.0690962829425514</v>
       </c>
       <c r="F12" s="3">
         <f>E12/SUM($E$12:$E$12)*100</f>
@@ -1436,7 +1443,7 @@
         <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>18</v>
@@ -1451,8 +1458,8 @@
         <v>Frontline Plc</v>
       </c>
       <c r="B17" s="3">
-        <f>Price_Data!H7</f>
-        <v>44.405997693194919</v>
+        <f>Price_Data!G7</f>
+        <v>15.29411764705883</v>
       </c>
       <c r="C17" t="str">
         <f>IF(B17&gt;0,"🟢","🔴")</f>
@@ -1469,16 +1476,16 @@
         <v>Antero Resources Corp</v>
       </c>
       <c r="B18" s="3">
-        <f>Price_Data!H8</f>
-        <v>-12.905043674274447</v>
+        <f>Price_Data!G8</f>
+        <v>13.347853142501553</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" ref="C18:C22" si="1">IF(B18&gt;0,"🟢","🔴")</f>
-        <v>🔴</v>
+        <v>🟢</v>
       </c>
       <c r="D18" t="str">
         <f t="shared" ref="D18:D22" si="2">IF(B18&gt;0,"🟢 보유","🔴 제외")</f>
-        <v>🔴 제외</v>
+        <v>🟢 보유</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1487,8 +1494,8 @@
         <v>금</v>
       </c>
       <c r="B19" s="3">
-        <f>Price_Data!H12</f>
-        <v>20.089787766191925</v>
+        <f>Price_Data!G9</f>
+        <v>21.247974068071311</v>
       </c>
       <c r="C19" t="str">
         <f>IF(B19&gt;0,"🟢","🔴")</f>
@@ -1505,8 +1512,8 @@
         <v>희토류</v>
       </c>
       <c r="B20" s="3">
-        <f>Price_Data!H9</f>
-        <v>86.064924782264455</v>
+        <f>Price_Data!G10</f>
+        <v>15.521064301552112</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="1"/>
@@ -1523,8 +1530,8 @@
         <v>구리</v>
       </c>
       <c r="B21" s="3">
-        <f>Price_Data!H10</f>
-        <v>9.4623655913978375</v>
+        <f>Price_Data!G11</f>
+        <v>1.8654230512991414</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="1"/>
@@ -1541,8 +1548,8 @@
         <v>우라늄</v>
       </c>
       <c r="B22" s="3">
-        <f>Price_Data!H11</f>
-        <v>17.378917378917382</v>
+        <f>Price_Data!G12</f>
+        <v>22.389047084879358</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="1"/>
@@ -1576,12 +1583,12 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B4" s="8">
         <v>80</v>
@@ -1676,64 +1683,64 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="32.875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
       <c r="B3" s="4">
-        <v>6600000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>9600000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B4" s="12">
         <f>Asset_Allocation!B4/100</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B5" s="13">
         <f>B3*B4</f>
-        <v>5280000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>7680000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B6" s="12">
         <f>Asset_Allocation!B14/100</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>47</v>
       </c>
       <c r="B7" s="14">
         <f>B5*B6</f>
-        <v>2640000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3840000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -1750,73 +1757,94 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>Price_Data!B2</f>
         <v>S&amp;P500</v>
       </c>
       <c r="B10" s="12">
         <f>Momentum_Calc!F5/100</f>
-        <v>0.26503768075386891</v>
+        <v>0.2726559484275124</v>
       </c>
       <c r="C10" s="12">
         <f>IF(Momentum_Calc!C5="🟢",B10,0)</f>
-        <v>0.26503768075386891</v>
+        <v>0.2726559484275124</v>
       </c>
       <c r="D10" s="13">
         <f>$B$7*C10</f>
-        <v>699699.47719021398</v>
+        <v>1046998.8419616476</v>
       </c>
       <c r="E10" t="str">
         <f>Price_Data!A2</f>
         <v>SPY</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>709180</v>
+      </c>
+      <c r="G10" s="13">
+        <f>D10-F10</f>
+        <v>337818.84196164762</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>Price_Data!B3</f>
         <v>KOSPI200</v>
       </c>
       <c r="B11" s="12">
         <f>Momentum_Calc!F6/100</f>
-        <v>0.52128380505674243</v>
+        <v>0.43603407740532807</v>
       </c>
       <c r="C11" s="12">
         <f>IF(Momentum_Calc!C6="🟢",B11,0)</f>
-        <v>0.52128380505674243</v>
+        <v>0.43603407740532807</v>
       </c>
       <c r="D11" s="13">
         <f>$B$7*C11</f>
-        <v>1376189.2453498</v>
+        <v>1674370.8572364599</v>
       </c>
       <c r="E11" t="str">
         <f>Price_Data!A3</f>
         <v>K51</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <v>1330000</v>
+      </c>
+      <c r="G11" s="13">
+        <f>D11-F11</f>
+        <v>344370.85723645985</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>Price_Data!B4</f>
-        <v>Bloomberg China Tech Select Top 10</v>
+        <v>TIGER 차이나테크 TOP10</v>
       </c>
       <c r="B12" s="12">
         <f>Momentum_Calc!F7/100</f>
-        <v>0.21367851418938863</v>
+        <v>0.29130997416715954</v>
       </c>
       <c r="C12" s="12">
         <f>IF(Momentum_Calc!C7="🟢",B12,0)</f>
-        <v>0.21367851418938863</v>
+        <v>0.29130997416715954</v>
       </c>
       <c r="D12" s="13">
         <f>$B$7*C12</f>
-        <v>564111.27745998593</v>
+        <v>1118630.3008018925</v>
       </c>
       <c r="E12" t="str">
         <f>Price_Data!A4</f>
-        <v>BCTST10T:IND</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0047A0</v>
+      </c>
+      <c r="F12">
+        <v>549610</v>
+      </c>
+      <c r="G12" s="13">
+        <f>D12-F12</f>
+        <v>569020.30080189253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>51</v>
       </c>
@@ -1826,7 +1854,7 @@
       </c>
       <c r="D13" s="14">
         <f>SUM(D10:D12)</f>
-        <v>2640000</v>
+        <v>3840000</v>
       </c>
     </row>
   </sheetData>
@@ -1837,7 +1865,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1845,21 +1873,21 @@
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
       <c r="B3" s="13">
         <f>Core_Allocation!B3</f>
-        <v>6600000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>9600000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -1868,16 +1896,16 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>54</v>
       </c>
       <c r="B5" s="14">
         <f>B3*B4</f>
-        <v>1320000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1920000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>55</v>
       </c>
@@ -1894,7 +1922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1908,13 +1936,20 @@
       </c>
       <c r="D8" s="13">
         <f>$B$5*C8</f>
-        <v>1320000</v>
+        <v>1920000</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>1324670</v>
+      </c>
+      <c r="G8" s="13">
+        <f>D8-F8</f>
+        <v>595330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>51</v>
       </c>
@@ -1924,7 +1959,7 @@
       </c>
       <c r="D9" s="14">
         <f>SUM(D8:D8)</f>
-        <v>1320000</v>
+        <v>1920000</v>
       </c>
     </row>
   </sheetData>
@@ -1935,7 +1970,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1943,21 +1978,21 @@
     <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
       <c r="B3" s="13">
         <f>Core_Allocation!B3</f>
-        <v>6600000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9600000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1966,16 +2001,16 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>46</v>
       </c>
       <c r="B5" s="13">
         <f>B3*B4</f>
-        <v>5280000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>7680000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -1984,123 +2019,144 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="14">
         <f>B5*B6</f>
-        <v>2640000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>3840000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>Price_Data!B7</f>
         <v>Frontline Plc</v>
       </c>
       <c r="B10" s="12">
         <f>Momentum_Calc!B17/100</f>
-        <v>0.44405997693194921</v>
+        <v>0.1529411764705883</v>
       </c>
       <c r="C10" t="str">
         <f>Momentum_Calc!C17</f>
         <v>🟢</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" s="15">
         <v>0.33300000000000002</v>
       </c>
       <c r="F10" s="13">
         <f>$B$7*E10</f>
-        <v>879120</v>
+        <v>1278720</v>
       </c>
       <c r="G10" t="str">
         <f>Price_Data!A7</f>
         <v>FRO</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>912648</v>
+      </c>
+      <c r="I10" s="13">
+        <f>F10-H10</f>
+        <v>366072</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>Price_Data!B8</f>
         <v>Antero Resources Corp</v>
       </c>
       <c r="B11" s="12">
         <f>Momentum_Calc!B18/100</f>
-        <v>-0.12905043674274447</v>
+        <v>0.13347853142501553</v>
       </c>
       <c r="C11" t="str">
         <f>Momentum_Calc!C18</f>
-        <v>🔴</v>
+        <v>🟢</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E11" s="15">
         <v>0.33300000000000002</v>
       </c>
       <c r="F11" s="13">
         <f>$B$7*E11</f>
-        <v>879120</v>
+        <v>1278720</v>
       </c>
       <c r="G11" t="str">
         <f>Price_Data!A8</f>
         <v>AR</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <v>1006348</v>
+      </c>
+      <c r="I11" s="13">
+        <f>F11-H11</f>
+        <v>272372</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>Price_Data!B12</f>
         <v>금</v>
       </c>
       <c r="B12" s="12">
         <f>Momentum_Calc!B19/100</f>
-        <v>0.20089787766191924</v>
+        <v>0.21247974068071313</v>
       </c>
       <c r="C12" t="str">
         <f>Momentum_Calc!C19</f>
         <v>🟢</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" s="15">
         <v>0.33300000000000002</v>
       </c>
       <c r="F12" s="13">
         <f>$B$7*E12</f>
-        <v>879120</v>
+        <v>1278720</v>
       </c>
       <c r="G12" t="str">
         <f>Price_Data!A12</f>
         <v>GC1</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>939080</v>
+      </c>
+      <c r="I12" s="13">
+        <f>F12-H12</f>
+        <v>339640</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>51</v>
       </c>
@@ -2110,7 +2166,7 @@
       </c>
       <c r="F13" s="14">
         <f>SUM(F10:F12)</f>
-        <v>2637360</v>
+        <v>3836160</v>
       </c>
     </row>
   </sheetData>
@@ -2135,12 +2191,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" s="22">
         <v>45965</v>
@@ -2148,7 +2204,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2159,29 +2215,29 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -2198,15 +2254,15 @@
       </c>
       <c r="D6" s="16">
         <f>Price_Data!C2</f>
-        <v>6840.2</v>
+        <v>6644.31</v>
       </c>
       <c r="E6" s="13">
         <f t="shared" ref="E6:E12" si="0">C6*D6</f>
-        <v>68402</v>
+        <v>66443.100000000006</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" ref="F6:F12" si="1">E6/SUM($E$6:$E$12)</f>
-        <v>3.1277930398031124E-2</v>
+        <v>2.0416242065107938E-2</v>
       </c>
       <c r="H6" s="12" t="e">
         <f>Core_Allocation!D10/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2214,15 +2270,15 @@
       </c>
       <c r="I6" s="13">
         <f>Core_Allocation!D10</f>
-        <v>699699.47719021398</v>
+        <v>1046998.8419616476</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" ref="J6:J12" si="2">I6-E6</f>
-        <v>631297.47719021398</v>
+        <v>980555.74196164764</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="3">IF(J6&gt;50000,"매수 ₩"&amp;TEXT(J6,"#,##0"),IF(J6&lt;-50000,"매도 ₩"&amp;TEXT(ABS(J6),"#,##0"),"유지"))</f>
-        <v>매수 ₩631,297</v>
+        <v>매수 ₩980,556</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -2239,15 +2295,15 @@
       </c>
       <c r="D7" s="16">
         <f>Price_Data!C3</f>
-        <v>579.46</v>
+        <v>554</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" si="0"/>
-        <v>202811</v>
+        <v>193900</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>9.2738638372490426E-2</v>
+        <v>5.9580443062175435E-2</v>
       </c>
       <c r="H7" s="12" t="e">
         <f>Core_Allocation!D11/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2255,40 +2311,40 @@
       </c>
       <c r="I7" s="13">
         <f>Core_Allocation!D11</f>
-        <v>1376189.2453498</v>
+        <v>1674370.8572364599</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="2"/>
-        <v>1173378.2453498</v>
+        <v>1480470.8572364599</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="3"/>
-        <v>매수 ₩1,173,378</v>
+        <v>매수 ₩1,480,471</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>Price_Data!B4</f>
-        <v>Bloomberg China Tech Select Top 10</v>
+        <v>TIGER 차이나테크 TOP10</v>
       </c>
       <c r="B8" t="str">
         <f>Price_Data!A4</f>
-        <v>BCTST10T:IND</v>
+        <v>0047A0</v>
       </c>
       <c r="C8" s="11">
         <v>100</v>
       </c>
       <c r="D8" s="16">
         <f>Price_Data!C4</f>
-        <v>2061.3200000000002</v>
+        <v>12770</v>
       </c>
       <c r="E8" s="13">
         <f t="shared" si="0"/>
-        <v>206132.00000000003</v>
+        <v>1277000</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>9.4257219800692266E-2</v>
+        <v>0.39238899324599291</v>
       </c>
       <c r="H8" s="12" t="e">
         <f>Core_Allocation!D12/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2296,15 +2352,15 @@
       </c>
       <c r="I8" s="13">
         <f>Core_Allocation!D12</f>
-        <v>564111.27745998593</v>
+        <v>1118630.3008018925</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="2"/>
-        <v>357979.27745998593</v>
+        <v>-158369.69919810747</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="3"/>
-        <v>매수 ₩357,979</v>
+        <v>매도 ₩158,370</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -2321,15 +2377,15 @@
       </c>
       <c r="D9" s="16">
         <f>Price_Data!C5</f>
-        <v>90.29</v>
+        <v>90.21</v>
       </c>
       <c r="E9" s="13">
         <f t="shared" si="0"/>
-        <v>4514.5</v>
+        <v>4510.5</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>2.0643287737480117E-3</v>
+        <v>1.3859597134189907E-3</v>
       </c>
       <c r="H9" s="12" t="e">
         <f>Core_Allocation!#REF!/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2362,14 +2418,14 @@
       </c>
       <c r="D10" s="16">
         <f>Price_Data!C7</f>
-        <v>25.04</v>
+        <v>23.52</v>
       </c>
       <c r="E10" s="13">
         <v>779605</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>0.35648710458695732</v>
+        <v>0.23955240491741764</v>
       </c>
       <c r="H10" s="12" t="e">
         <f>Bond_Allocation!D8/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2377,15 +2433,15 @@
       </c>
       <c r="I10" s="13">
         <f>Bond_Allocation!D8</f>
-        <v>1320000</v>
+        <v>1920000</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="2"/>
-        <v>540395</v>
+        <v>1140395</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="3"/>
-        <v>매수 ₩540,395</v>
+        <v>매수 ₩1,140,395</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -2402,14 +2458,14 @@
       </c>
       <c r="D11" s="16">
         <f>Price_Data!C8</f>
-        <v>30.91</v>
+        <v>36.43</v>
       </c>
       <c r="E11" s="13">
         <v>805312</v>
       </c>
       <c r="F11" s="12">
         <f t="shared" si="1"/>
-        <v>0.36824204971637142</v>
+        <v>0.2474514995527933</v>
       </c>
       <c r="H11" s="12" t="e">
         <f>Bond_Allocation!#REF!/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2442,15 +2498,15 @@
       </c>
       <c r="D12" s="16">
         <f>Price_Data!C12</f>
-        <v>4004.43</v>
+        <v>4255.1000000000004</v>
       </c>
       <c r="E12" s="13">
         <f t="shared" si="0"/>
-        <v>120132.9</v>
+        <v>127653.00000000001</v>
       </c>
       <c r="F12" s="12">
         <f t="shared" si="1"/>
-        <v>5.4932728351709495E-2</v>
+        <v>3.9224457443093767E-2</v>
       </c>
       <c r="H12" s="12" t="e">
         <f>Satellite_Selection!F10/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2458,15 +2514,15 @@
       </c>
       <c r="I12" s="13">
         <f>Satellite_Selection!F10</f>
-        <v>879120</v>
+        <v>1278720</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="2"/>
-        <v>758987.1</v>
+        <v>1151067</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="3"/>
-        <v>매수 ₩758,987</v>
+        <v>매수 ₩1,151,067</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -2475,11 +2531,11 @@
       </c>
       <c r="E13" s="14">
         <f>SUM(E6:E12)</f>
-        <v>2186909.4</v>
+        <v>3254423.6</v>
       </c>
       <c r="F13" s="17">
         <f>SUM(F6:F12)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="I13" s="14" t="e">
         <f>SUM(I6:I12)</f>
@@ -2488,27 +2544,27 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2527,27 +2583,27 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>10</v>
@@ -2555,42 +2611,42 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4" s="4">
         <v>30000000</v>
       </c>
       <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
         <v>87</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>89</v>
-      </c>
       <c r="F4" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B5" s="13">
         <f>Rebalancing!E13</f>
-        <v>2186909.4</v>
+        <v>3254423.6</v>
       </c>
       <c r="C5" s="12">
         <f>(B5-B4)/B4</f>
-        <v>-0.92710302</v>
+        <v>-0.89151921333333328</v>
       </c>
       <c r="D5" s="12">
         <f>(B5-B$4)/B$4</f>
-        <v>-0.92710302</v>
+        <v>-0.89151921333333328</v>
       </c>
       <c r="E5" s="12">
         <f>Asset_Allocation!B4/100</f>
@@ -2622,12 +2678,12 @@
   <sheetData>
     <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.5">
       <c r="A1" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B2" s="23">
         <f>Rebalancing!B2</f>
@@ -2636,7 +2692,7 @@
     </row>
     <row r="4" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2645,48 +2701,48 @@
       </c>
       <c r="B5" s="20">
         <f>Rebalancing!E13</f>
-        <v>2186909.4</v>
+        <v>3254423.6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B6" s="12">
         <f>Performance!C5</f>
-        <v>-0.92710302</v>
+        <v>-0.89151921333333328</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B7" s="12">
         <f>Performance!D5</f>
-        <v>-0.92710302</v>
+        <v>-0.89151921333333328</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B10" s="21">
         <f>SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"S&amp;P500")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"KOSPI")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"CSI300")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Europe")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Apple")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Tesla")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Exxon")</f>
-        <v>68402</v>
+        <v>66443.100000000006</v>
       </c>
       <c r="C10" s="12">
         <f>B10/B5</f>
-        <v>3.1277930398031124E-2</v>
+        <v>2.0416242065107938E-2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" s="21">
         <f>SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"미국채")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"한국채")</f>
@@ -2699,20 +2755,20 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="21">
         <f>SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"S&amp;P500")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"KOSPI")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"CSI300")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Europe")</f>
-        <v>68402</v>
+        <v>66443.100000000006</v>
       </c>
       <c r="C13" s="12">
         <f>B13/B5</f>
-        <v>3.1277930398031124E-2</v>
+        <v>2.0416242065107938E-2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B14" s="21">
         <f>SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Apple")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Tesla")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Exxon")</f>
@@ -2725,21 +2781,21 @@
     </row>
     <row r="16" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -2749,14 +2805,14 @@
       </c>
       <c r="B18" s="13">
         <f>Rebalancing!E6</f>
-        <v>68402</v>
+        <v>66443.100000000006</v>
       </c>
       <c r="C18" s="12">
         <f>Rebalancing!F6</f>
-        <v>3.1277930398031124E-2</v>
+        <v>2.0416242065107938E-2</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -2766,31 +2822,31 @@
       </c>
       <c r="B19" s="13">
         <f>Rebalancing!E7</f>
-        <v>202811</v>
+        <v>193900</v>
       </c>
       <c r="C19" s="12">
         <f>Rebalancing!F7</f>
-        <v>9.2738638372490426E-2</v>
+        <v>5.9580443062175435E-2</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>Rebalancing!A8</f>
-        <v>Bloomberg China Tech Select Top 10</v>
+        <v>TIGER 차이나테크 TOP10</v>
       </c>
       <c r="B20" s="13">
         <f>Rebalancing!E8</f>
-        <v>206132.00000000003</v>
+        <v>1277000</v>
       </c>
       <c r="C20" s="12">
         <f>Rebalancing!F8</f>
-        <v>9.4257219800692266E-2</v>
+        <v>0.39238899324599291</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -2800,14 +2856,14 @@
       </c>
       <c r="B21" s="13">
         <f>Rebalancing!E9</f>
-        <v>4514.5</v>
+        <v>4510.5</v>
       </c>
       <c r="C21" s="12">
         <f>Rebalancing!F9</f>
-        <v>2.0643287737480117E-3</v>
+        <v>1.3859597134189907E-3</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -2821,10 +2877,10 @@
       </c>
       <c r="C22" s="12">
         <f>Rebalancing!F10</f>
-        <v>0.35648710458695732</v>
+        <v>0.23955240491741764</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -2838,10 +2894,10 @@
       </c>
       <c r="C23" s="12">
         <f>Rebalancing!F11</f>
-        <v>0.36824204971637142</v>
+        <v>0.2474514995527933</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -2851,14 +2907,14 @@
       </c>
       <c r="B24" s="13">
         <f>Rebalancing!E12</f>
-        <v>120132.9</v>
+        <v>127653.00000000001</v>
       </c>
       <c r="C24" s="12">
         <f>Rebalancing!F12</f>
-        <v>5.4932728351709495E-2</v>
+        <v>3.9224457443093767E-2</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio/Portfolio_Rebalancing_Template.xlsx
+++ b/Portfolio/Portfolio_Rebalancing_Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29630"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KoreaPDS\Work\macro_strategy\Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://goe0200-my.sharepoint.com/personal/wngml0630_kwangsunge_goe_go_kr/Documents/macro_strategy/Portfolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="59" documentId="11_8C0B8BEF93006CC2432FAC54C2245937AAE96A49" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22F057F7-FF11-4715-A586-0AE9EAC6E509}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="8"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Price_Data" sheetId="1" r:id="rId1"/>
@@ -42,12 +43,12 @@
     <definedName name="TreeMap">"TreeMap"</definedName>
     <definedName name="Waterfall">"Waterfall"</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="127">
   <si>
     <t>Ticker</t>
   </si>
@@ -386,10 +387,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>우라늄</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>희토류</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -406,10 +403,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>URANIUM</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>K51</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -447,13 +440,25 @@
   </si>
   <si>
     <t>TIGER 차이나테크 TOP10</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>상</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>URNM</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sportt Uranium Miners ETF</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0.0&quot;%&quot;"/>
     <numFmt numFmtId="177" formatCode="0.0000"/>
@@ -878,16 +883,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
     <col min="3" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -916,7 +921,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -924,95 +929,95 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>6644.31</v>
+        <v>6865.17</v>
       </c>
       <c r="D2" s="2">
-        <v>6415.54</v>
+        <v>6715.35</v>
       </c>
       <c r="E2" s="2">
-        <v>5935.94</v>
+        <v>6227.42</v>
       </c>
       <c r="F2" s="2">
-        <v>6047.15</v>
+        <v>5868.55</v>
       </c>
       <c r="G2" s="3">
         <f t="shared" ref="G2:G8" si="0">(C2-D2)/D2*100</f>
-        <v>3.5658728649498004</v>
+        <v>2.2310080636154437</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" ref="H2:H8" si="1">(C2-E2)/E2*100</f>
-        <v>11.933577495729418</v>
+        <v>10.240998680031216</v>
       </c>
       <c r="I2" s="3">
         <f t="shared" ref="I2:I8" si="2">(C2-F2)/F2*100</f>
-        <v>9.8750651133178575</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>16.982389176201956</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
         <v>103</v>
       </c>
       <c r="C3" s="2">
-        <v>554</v>
+        <v>624</v>
       </c>
       <c r="D3" s="2">
-        <v>423</v>
+        <v>493</v>
       </c>
       <c r="E3" s="2">
-        <v>360</v>
+        <v>414</v>
       </c>
       <c r="F3" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" si="0"/>
-        <v>30.969267139479907</v>
+        <v>26.572008113590261</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" si="1"/>
-        <v>53.888888888888886</v>
+        <v>50.724637681159422</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" si="2"/>
-        <v>70.461538461538467</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>96.226415094339629</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C4" s="2">
-        <v>12770</v>
+        <v>12370</v>
       </c>
       <c r="D4" s="2">
-        <v>11929</v>
+        <v>14309</v>
       </c>
       <c r="E4" s="2">
-        <v>9275</v>
+        <v>9345</v>
       </c>
       <c r="F4" s="2">
         <v>10138</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" ref="G4" si="3">(C4-D4)/D4*100</f>
-        <v>7.0500461061279234</v>
+        <v>-13.550912013418129</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ref="H4" si="4">(C4-E4)/E4*100</f>
-        <v>37.681940700808624</v>
+        <v>32.37025147137507</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" ref="I4" si="5">(C4-F4)/F4*100</f>
-        <v>25.961728151509174</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>22.016176760702308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1020,31 +1025,31 @@
         <v>13</v>
       </c>
       <c r="C5" s="2">
-        <v>90.21</v>
+        <v>87.06</v>
       </c>
       <c r="D5" s="2">
-        <v>86.28</v>
+        <v>88.57</v>
       </c>
       <c r="E5" s="2">
-        <v>83.49</v>
+        <v>85.66</v>
       </c>
       <c r="F5" s="2">
-        <v>90.33</v>
+        <v>93.27</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>4.5549374130737048</v>
+        <v>-1.7048662075194658</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="1"/>
-        <v>8.0488681279195102</v>
+        <v>1.6343684333411226</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="2"/>
-        <v>-0.13284623048821492</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>-6.6580894178192285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
@@ -1052,7 +1057,7 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>104</v>
       </c>
@@ -1060,10 +1065,10 @@
         <v>105</v>
       </c>
       <c r="C7" s="2">
-        <v>23.52</v>
+        <v>20.57</v>
       </c>
       <c r="D7" s="2">
-        <v>20.399999999999999</v>
+        <v>22.51</v>
       </c>
       <c r="E7" s="2">
         <v>17.100000000000001</v>
@@ -1073,18 +1078,18 @@
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
-        <v>15.29411764705883</v>
+        <v>-8.6183918258551806</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="1"/>
-        <v>37.543859649122794</v>
+        <v>20.292397660818708</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="2"/>
-        <v>51.059730250481692</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>32.113037893384714</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -1092,10 +1097,10 @@
         <v>107</v>
       </c>
       <c r="C8" s="2">
-        <v>36.43</v>
+        <v>34.22</v>
       </c>
       <c r="D8" s="2">
-        <v>32.14</v>
+        <v>33.49</v>
       </c>
       <c r="E8" s="2">
         <v>38.97</v>
@@ -1105,23 +1110,23 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>13.347853142501553</v>
+        <v>2.1797551507912716</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="1"/>
-        <v>-6.5178342314600961</v>
+        <v>-12.188863228124198</v>
       </c>
       <c r="I8" s="3">
         <f t="shared" si="2"/>
-        <v>11.440807586417872</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4.6803303762618578</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2">
         <v>74.81</v>
@@ -1148,9 +1153,9 @@
         <v>66.912092815707283</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
         <v>109</v>
@@ -1180,18 +1185,18 @@
         <v>27.696078431372545</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2">
-        <v>76.45</v>
+        <v>60.35</v>
       </c>
       <c r="D11" s="2">
-        <v>75.05</v>
+        <v>59.01</v>
       </c>
       <c r="E11" s="2">
         <v>71.95</v>
@@ -1201,29 +1206,29 @@
       </c>
       <c r="G11" s="3">
         <f t="shared" ref="G11" si="6">(C11-D11)/D11*100</f>
-        <v>1.8654230512991414</v>
+        <v>2.270801559057793</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" ref="H11" si="7">(C11-E11)/E11*100</f>
-        <v>6.2543432939541344</v>
+        <v>-16.122307157748438</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" ref="I11" si="8">(C11-F11)/F11*100</f>
-        <v>-1.3548387096774157</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>-22.129032258064516</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
         <v>108</v>
       </c>
       <c r="C12" s="2">
-        <v>4255.1000000000004</v>
+        <v>4332.01</v>
       </c>
       <c r="D12" s="2">
-        <v>3476.7</v>
+        <v>3856.12</v>
       </c>
       <c r="E12" s="2">
         <v>3381.7</v>
@@ -1233,15 +1238,15 @@
       </c>
       <c r="G12" s="3">
         <f>(C12-D12)/D12*100</f>
-        <v>22.389047084879358</v>
+        <v>12.34116158210845</v>
       </c>
       <c r="H12" s="3">
         <f>(C12-E12)/E12*100</f>
-        <v>25.827246651092661</v>
+        <v>28.10154655942279</v>
       </c>
       <c r="I12" s="3">
         <f>(C12-F12)/F12*100</f>
-        <v>61.043217609501141</v>
+        <v>63.954038475367213</v>
       </c>
     </row>
   </sheetData>
@@ -1251,31 +1256,31 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="24.75" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="14" customWidth="1"/>
     <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="20.65" x14ac:dyDescent="0.7">
       <c r="A1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
@@ -1296,13 +1301,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="3">
         <f>Price_Data!G2</f>
-        <v>3.5658728649498004</v>
+        <v>2.2310080636154437</v>
       </c>
       <c r="C5" t="str">
         <f>IF(B5&gt;0,"🟢","🔴")</f>
@@ -1310,24 +1315,24 @@
       </c>
       <c r="D5" s="3">
         <f>IF(B5&gt;0,B5,0)</f>
-        <v>3.5658728649498004</v>
+        <v>2.2310080636154437</v>
       </c>
       <c r="E5" s="9">
         <f>(1+D5/100)^$K$4</f>
-        <v>1.0725890022278946</v>
+        <v>1.0451179009703007</v>
       </c>
       <c r="F5" s="3">
-        <f>E5/SUM($E$5:$E$7)*100</f>
-        <v>27.265594842751241</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <f>E5/SUM($E$5:$E$6)*100</f>
+        <v>39.480644849611487</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="3">
         <f>Price_Data!G3</f>
-        <v>30.969267139479907</v>
+        <v>26.572008113590261</v>
       </c>
       <c r="C6" t="str">
         <f>IF(B6&gt;0,"🟢","🔴")</f>
@@ -1335,59 +1340,58 @@
       </c>
       <c r="D6" s="3">
         <f>IF(B6&gt;0,B6,0)</f>
-        <v>30.969267139479907</v>
+        <v>26.572008113590261</v>
       </c>
       <c r="E6" s="9">
         <f>(1+D6/100)^$K$4</f>
-        <v>1.7152948935052448</v>
+        <v>1.6020473237906758</v>
       </c>
       <c r="F6" s="3">
-        <f t="shared" ref="F6:F7" si="0">E6/SUM($E$5:$E$7)*100</f>
-        <v>43.603407740532809</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <f>E6/SUM($E$5:$E$6)*100</f>
+        <v>60.51935515038852</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A7" t="str">
         <f>Price_Data!B4</f>
         <v>TIGER 차이나테크 TOP10</v>
       </c>
       <c r="B7" s="3">
         <f>Price_Data!G4</f>
-        <v>7.0500461061279234</v>
+        <v>-13.550912013418129</v>
       </c>
       <c r="C7" t="str">
         <f>IF(B7&gt;0,"🟢","🔴")</f>
-        <v>🟢</v>
+        <v>🔴</v>
       </c>
       <c r="D7" s="3">
         <f>IF(B7&gt;0,B7,0)</f>
-        <v>7.0500461061279234</v>
+        <v>0</v>
       </c>
       <c r="E7" s="9">
         <f>(1+D7/100)^$K$4</f>
-        <v>1.1459712371324113</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3">
-        <f t="shared" si="0"/>
-        <v>29.130997416715953</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
       <c r="D8" s="3"/>
       <c r="E8" s="9"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A10" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
@@ -1408,42 +1412,42 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="3">
         <f>Price_Data!G5</f>
-        <v>4.5549374130737048</v>
+        <v>-1.7048662075194658</v>
       </c>
       <c r="C12" t="str">
         <f>IF(B12&gt;0,"🟢","🔴")</f>
-        <v>🟢</v>
+        <v>🔴</v>
       </c>
       <c r="D12" s="3">
         <f>IF(B12&gt;0,B12,0)</f>
-        <v>4.5549374130737048</v>
+        <v>0</v>
       </c>
       <c r="E12" s="9">
         <f>(1+D12/100)^$K$11</f>
-        <v>1.0690962829425514</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3">
         <f>E12/SUM($E$12:$E$12)*100</f>
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A15" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>18</v>
@@ -1452,43 +1456,43 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A17" t="str">
         <f>Price_Data!B7</f>
         <v>Frontline Plc</v>
       </c>
       <c r="B17" s="3">
         <f>Price_Data!G7</f>
-        <v>15.29411764705883</v>
+        <v>-8.6183918258551806</v>
       </c>
       <c r="C17" t="str">
         <f>IF(B17&gt;0,"🟢","🔴")</f>
-        <v>🟢</v>
+        <v>🔴</v>
       </c>
       <c r="D17" t="str">
         <f>IF(B17&gt;0,"🟢 보유","🔴 제외")</f>
-        <v>🟢 보유</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>🔴 제외</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A18" t="str">
         <f>Price_Data!B8</f>
         <v>Antero Resources Corp</v>
       </c>
       <c r="B18" s="3">
         <f>Price_Data!G8</f>
-        <v>13.347853142501553</v>
+        <v>2.1797551507912716</v>
       </c>
       <c r="C18" t="str">
-        <f t="shared" ref="C18:C22" si="1">IF(B18&gt;0,"🟢","🔴")</f>
+        <f t="shared" ref="C18:C22" si="0">IF(B18&gt;0,"🟢","🔴")</f>
         <v>🟢</v>
       </c>
       <c r="D18" t="str">
-        <f t="shared" ref="D18:D22" si="2">IF(B18&gt;0,"🟢 보유","🔴 제외")</f>
+        <f t="shared" ref="D18:D22" si="1">IF(B18&gt;0,"🟢 보유","🔴 제외")</f>
         <v>🟢 보유</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A19" t="str">
         <f>Price_Data!B12</f>
         <v>금</v>
@@ -1502,11 +1506,11 @@
         <v>🟢</v>
       </c>
       <c r="D19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>🟢 보유</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A20" t="str">
         <f>Price_Data!B9</f>
         <v>희토류</v>
@@ -1516,47 +1520,47 @@
         <v>15.521064301552112</v>
       </c>
       <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢</v>
+      </c>
+      <c r="D20" t="str">
         <f t="shared" si="1"/>
-        <v>🟢</v>
-      </c>
-      <c r="D20" t="str">
-        <f t="shared" si="2"/>
         <v>🟢 보유</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A21" t="str">
         <f>Price_Data!B10</f>
         <v>구리</v>
       </c>
       <c r="B21" s="3">
         <f>Price_Data!G11</f>
-        <v>1.8654230512991414</v>
+        <v>2.270801559057793</v>
       </c>
       <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢</v>
+      </c>
+      <c r="D21" t="str">
         <f t="shared" si="1"/>
-        <v>🟢</v>
-      </c>
-      <c r="D21" t="str">
-        <f t="shared" si="2"/>
         <v>🟢 보유</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A22" t="str">
         <f>Price_Data!B11</f>
-        <v>우라늄</v>
+        <v>Sportt Uranium Miners ETF</v>
       </c>
       <c r="B22" s="3">
         <f>Price_Data!G12</f>
-        <v>22.389047084879358</v>
+        <v>12.34116158210845</v>
       </c>
       <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>🟢</v>
+      </c>
+      <c r="D22" t="str">
         <f t="shared" si="1"/>
-        <v>🟢</v>
-      </c>
-      <c r="D22" t="str">
-        <f t="shared" si="2"/>
         <v>🟢 보유</v>
       </c>
     </row>
@@ -1567,28 +1571,28 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="20.65" x14ac:dyDescent="0.7">
       <c r="A1" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B4" s="8">
         <v>80</v>
@@ -1597,7 +1601,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1609,12 +1613,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.6">
       <c r="A7" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1622,7 +1626,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -1630,7 +1634,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1638,12 +1642,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.6"/>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1654,7 +1659,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1666,13 +1671,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A17" s="7"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.6">
       <c r="B18" s="11"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.6">
       <c r="B19" s="11"/>
     </row>
   </sheetData>
@@ -1682,65 +1687,66 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="32.875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="20.65" x14ac:dyDescent="0.7">
       <c r="A1" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>44</v>
       </c>
       <c r="B3" s="4">
-        <v>9600000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <f>9600000+3000000</f>
+        <v>12600000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B4" s="12">
         <f>Asset_Allocation!B4/100</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B5" s="13">
         <f>B3*B4</f>
-        <v>7680000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10080000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B6" s="12">
         <f>Asset_Allocation!B14/100</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>47</v>
       </c>
       <c r="B7" s="14">
         <f>B5*B6</f>
-        <v>3840000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>5040000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -1757,22 +1763,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A10" t="str">
         <f>Price_Data!B2</f>
         <v>S&amp;P500</v>
       </c>
       <c r="B10" s="12">
         <f>Momentum_Calc!F5/100</f>
-        <v>0.2726559484275124</v>
+        <v>0.39480644849611485</v>
       </c>
       <c r="C10" s="12">
         <f>IF(Momentum_Calc!C5="🟢",B10,0)</f>
-        <v>0.2726559484275124</v>
+        <v>0.39480644849611485</v>
       </c>
       <c r="D10" s="13">
         <f>$B$7*C10</f>
-        <v>1046998.8419616476</v>
+        <v>1989824.5004204188</v>
       </c>
       <c r="E10" t="str">
         <f>Price_Data!A2</f>
@@ -1783,25 +1789,25 @@
       </c>
       <c r="G10" s="13">
         <f>D10-F10</f>
-        <v>337818.84196164762</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1280644.5004204188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A11" t="str">
         <f>Price_Data!B3</f>
         <v>KOSPI200</v>
       </c>
       <c r="B11" s="12">
         <f>Momentum_Calc!F6/100</f>
-        <v>0.43603407740532807</v>
+        <v>0.60519355150388521</v>
       </c>
       <c r="C11" s="12">
         <f>IF(Momentum_Calc!C6="🟢",B11,0)</f>
-        <v>0.43603407740532807</v>
+        <v>0.60519355150388521</v>
       </c>
       <c r="D11" s="13">
         <f>$B$7*C11</f>
-        <v>1674370.8572364599</v>
+        <v>3050175.4995795814</v>
       </c>
       <c r="E11" t="str">
         <f>Price_Data!A3</f>
@@ -1812,25 +1818,25 @@
       </c>
       <c r="G11" s="13">
         <f>D11-F11</f>
-        <v>344370.85723645985</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1720175.4995795814</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A12" t="str">
         <f>Price_Data!B4</f>
         <v>TIGER 차이나테크 TOP10</v>
       </c>
       <c r="B12" s="12">
         <f>Momentum_Calc!F7/100</f>
-        <v>0.29130997416715954</v>
+        <v>0</v>
       </c>
       <c r="C12" s="12">
         <f>IF(Momentum_Calc!C7="🟢",B12,0)</f>
-        <v>0.29130997416715954</v>
+        <v>0</v>
       </c>
       <c r="D12" s="13">
         <f>$B$7*C12</f>
-        <v>1118630.3008018925</v>
+        <v>0</v>
       </c>
       <c r="E12" t="str">
         <f>Price_Data!A4</f>
@@ -1841,10 +1847,10 @@
       </c>
       <c r="G12" s="13">
         <f>D12-F12</f>
-        <v>569020.30080189253</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>-549610</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A13" s="7" t="s">
         <v>51</v>
       </c>
@@ -1854,7 +1860,7 @@
       </c>
       <c r="D13" s="14">
         <f>SUM(D10:D12)</f>
-        <v>3840000</v>
+        <v>5040000</v>
       </c>
     </row>
   </sheetData>
@@ -1864,30 +1870,30 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="20.65" x14ac:dyDescent="0.7">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>44</v>
       </c>
       <c r="B3" s="13">
         <f>Core_Allocation!B3</f>
-        <v>9600000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12600000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -1896,16 +1902,16 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>54</v>
       </c>
       <c r="B5" s="14">
         <f>B3*B4</f>
-        <v>1920000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2520000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A7" s="1" t="s">
         <v>55</v>
       </c>
@@ -1922,7 +1928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1936,7 +1942,7 @@
       </c>
       <c r="D8" s="13">
         <f>$B$5*C8</f>
-        <v>1920000</v>
+        <v>2520000</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -1946,10 +1952,10 @@
       </c>
       <c r="G8" s="13">
         <f>D8-F8</f>
-        <v>595330</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1195330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A9" s="7" t="s">
         <v>51</v>
       </c>
@@ -1959,7 +1965,7 @@
       </c>
       <c r="D9" s="14">
         <f>SUM(D8:D8)</f>
-        <v>1920000</v>
+        <v>2520000</v>
       </c>
     </row>
   </sheetData>
@@ -1969,30 +1975,30 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="20.65" x14ac:dyDescent="0.7">
       <c r="A1" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>44</v>
       </c>
       <c r="B3" s="13">
         <f>Core_Allocation!B3</f>
-        <v>9600000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>12600000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -2001,16 +2007,16 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>46</v>
       </c>
       <c r="B5" s="13">
         <f>B3*B4</f>
-        <v>7680000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10080000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -2019,21 +2025,21 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="14">
         <f>B5*B6</f>
-        <v>3840000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5040000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
@@ -2051,28 +2057,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A10" t="str">
         <f>Price_Data!B7</f>
         <v>Frontline Plc</v>
       </c>
       <c r="B10" s="12">
         <f>Momentum_Calc!B17/100</f>
-        <v>0.1529411764705883</v>
+        <v>-8.6183918258551803E-2</v>
       </c>
       <c r="C10" t="str">
         <f>Momentum_Calc!C17</f>
-        <v>🟢</v>
+        <v>🔴</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="E10" s="15">
-        <v>0.33300000000000002</v>
+        <v>0.25</v>
       </c>
       <c r="F10" s="13">
         <f>$B$7*E10</f>
-        <v>1278720</v>
+        <v>1260000</v>
       </c>
       <c r="G10" t="str">
         <f>Price_Data!A7</f>
@@ -2083,31 +2089,31 @@
       </c>
       <c r="I10" s="13">
         <f>F10-H10</f>
-        <v>366072</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>347352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A11" t="str">
         <f>Price_Data!B8</f>
         <v>Antero Resources Corp</v>
       </c>
       <c r="B11" s="12">
         <f>Momentum_Calc!B18/100</f>
-        <v>0.13347853142501553</v>
+        <v>2.1797551507912717E-2</v>
       </c>
       <c r="C11" t="str">
         <f>Momentum_Calc!C18</f>
         <v>🟢</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E11" s="15">
-        <v>0.33300000000000002</v>
+        <v>0.25</v>
       </c>
       <c r="F11" s="13">
         <f>$B$7*E11</f>
-        <v>1278720</v>
+        <v>1260000</v>
       </c>
       <c r="G11" t="str">
         <f>Price_Data!A8</f>
@@ -2118,10 +2124,10 @@
       </c>
       <c r="I11" s="13">
         <f>F11-H11</f>
-        <v>272372</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>253652</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A12" t="str">
         <f>Price_Data!B12</f>
         <v>금</v>
@@ -2138,11 +2144,11 @@
         <v>63</v>
       </c>
       <c r="E12" s="15">
-        <v>0.33300000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="F12" s="13">
         <f>$B$7*E12</f>
-        <v>1278720</v>
+        <v>2016000</v>
       </c>
       <c r="G12" t="str">
         <f>Price_Data!A12</f>
@@ -2153,20 +2159,49 @@
       </c>
       <c r="I12" s="13">
         <f>F12-H12</f>
-        <v>339640</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+        <v>1076920</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A13" t="str">
+        <f>Price_Data!B11</f>
+        <v>Sportt Uranium Miners ETF</v>
+      </c>
+      <c r="B13" s="12">
+        <f>Momentum_Calc!B22/100</f>
+        <v>0.12341161582108449</v>
+      </c>
+      <c r="C13" t="str">
+        <f>Momentum_Calc!C22</f>
+        <v>🟢</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="F13" s="13">
+        <f>$B$7*E13</f>
+        <v>504000</v>
+      </c>
+      <c r="G13" t="str">
+        <f>Price_Data!A11</f>
+        <v>URNM</v>
+      </c>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A14" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="12">
-        <f>SUM(E10:E12)</f>
-        <v>0.99900000000000011</v>
-      </c>
-      <c r="F13" s="14">
+      <c r="E14" s="12">
+        <f>SUM(E10:E13)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="14">
         <f>SUM(F10:F12)</f>
-        <v>3836160</v>
+        <v>4536000</v>
       </c>
     </row>
   </sheetData>
@@ -2177,9 +2212,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
@@ -2189,12 +2224,12 @@
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="20.65" x14ac:dyDescent="0.7">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -2202,12 +2237,12 @@
         <v>45965</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A4" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -2240,7 +2275,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A6" t="str">
         <f>Price_Data!B2</f>
         <v>S&amp;P500</v>
@@ -2254,15 +2289,15 @@
       </c>
       <c r="D6" s="16">
         <f>Price_Data!C2</f>
-        <v>6644.31</v>
+        <v>6865.17</v>
       </c>
       <c r="E6" s="13">
         <f t="shared" ref="E6:E12" si="0">C6*D6</f>
-        <v>66443.100000000006</v>
+        <v>68651.7</v>
       </c>
       <c r="F6" s="12">
         <f t="shared" ref="F6:F12" si="1">E6/SUM($E$6:$E$12)</f>
-        <v>2.0416242065107938E-2</v>
+        <v>2.1167354550113125E-2</v>
       </c>
       <c r="H6" s="12" t="e">
         <f>Core_Allocation!D10/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2270,18 +2305,18 @@
       </c>
       <c r="I6" s="13">
         <f>Core_Allocation!D10</f>
-        <v>1046998.8419616476</v>
+        <v>1989824.5004204188</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" ref="J6:J12" si="2">I6-E6</f>
-        <v>980555.74196164764</v>
+        <v>1921172.8004204188</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" ref="K6:K12" si="3">IF(J6&gt;50000,"매수 ₩"&amp;TEXT(J6,"#,##0"),IF(J6&lt;-50000,"매도 ₩"&amp;TEXT(ABS(J6),"#,##0"),"유지"))</f>
-        <v>매수 ₩980,556</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>매수 ₩1,921,173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A7" t="str">
         <f>Price_Data!B3</f>
         <v>KOSPI200</v>
@@ -2295,15 +2330,15 @@
       </c>
       <c r="D7" s="16">
         <f>Price_Data!C3</f>
-        <v>554</v>
+        <v>624</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" si="0"/>
-        <v>193900</v>
+        <v>218400</v>
       </c>
       <c r="F7" s="12">
         <f t="shared" si="1"/>
-        <v>5.9580443062175435E-2</v>
+        <v>6.7339195296616208E-2</v>
       </c>
       <c r="H7" s="12" t="e">
         <f>Core_Allocation!D11/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2311,18 +2346,18 @@
       </c>
       <c r="I7" s="13">
         <f>Core_Allocation!D11</f>
-        <v>1674370.8572364599</v>
+        <v>3050175.4995795814</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="2"/>
-        <v>1480470.8572364599</v>
+        <v>2831775.4995795814</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="3"/>
-        <v>매수 ₩1,480,471</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>매수 ₩2,831,775</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A8" t="str">
         <f>Price_Data!B4</f>
         <v>TIGER 차이나테크 TOP10</v>
@@ -2336,15 +2371,15 @@
       </c>
       <c r="D8" s="16">
         <f>Price_Data!C4</f>
-        <v>12770</v>
+        <v>12370</v>
       </c>
       <c r="E8" s="13">
         <f t="shared" si="0"/>
-        <v>1277000</v>
+        <v>1237000</v>
       </c>
       <c r="F8" s="12">
         <f t="shared" si="1"/>
-        <v>0.39238899324599291</v>
+        <v>0.38140377555821542</v>
       </c>
       <c r="H8" s="12" t="e">
         <f>Core_Allocation!D12/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2352,18 +2387,18 @@
       </c>
       <c r="I8" s="13">
         <f>Core_Allocation!D12</f>
-        <v>1118630.3008018925</v>
+        <v>0</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="2"/>
-        <v>-158369.69919810747</v>
+        <v>-1237000</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="3"/>
-        <v>매도 ₩158,370</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>매도 ₩1,237,000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A9" t="str">
         <f>Price_Data!B5</f>
         <v>미국채 20년</v>
@@ -2377,15 +2412,15 @@
       </c>
       <c r="D9" s="16">
         <f>Price_Data!C5</f>
-        <v>90.21</v>
+        <v>87.06</v>
       </c>
       <c r="E9" s="13">
         <f t="shared" si="0"/>
-        <v>4510.5</v>
+        <v>4353</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>1.3859597134189907E-3</v>
+        <v>1.3421589612004137E-3</v>
       </c>
       <c r="H9" s="12" t="e">
         <f>Core_Allocation!#REF!/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2404,7 +2439,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A10" t="str">
         <f>Price_Data!B7</f>
         <v>Frontline Plc</v>
@@ -2418,14 +2453,14 @@
       </c>
       <c r="D10" s="16">
         <f>Price_Data!C7</f>
-        <v>23.52</v>
+        <v>20.57</v>
       </c>
       <c r="E10" s="13">
         <v>779605</v>
       </c>
       <c r="F10" s="12">
         <f t="shared" si="1"/>
-        <v>0.23955240491741764</v>
+        <v>0.24037533584806994</v>
       </c>
       <c r="H10" s="12" t="e">
         <f>Bond_Allocation!D8/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2433,18 +2468,18 @@
       </c>
       <c r="I10" s="13">
         <f>Bond_Allocation!D8</f>
-        <v>1920000</v>
+        <v>2520000</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="2"/>
-        <v>1140395</v>
+        <v>1740395</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="3"/>
-        <v>매수 ₩1,140,395</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>매수 ₩1,740,395</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A11" t="str">
         <f>Price_Data!B8</f>
         <v>Antero Resources Corp</v>
@@ -2458,14 +2493,14 @@
       </c>
       <c r="D11" s="16">
         <f>Price_Data!C8</f>
-        <v>36.43</v>
+        <v>34.22</v>
       </c>
       <c r="E11" s="13">
         <v>805312</v>
       </c>
       <c r="F11" s="12">
         <f t="shared" si="1"/>
-        <v>0.2474514995527933</v>
+        <v>0.2483015661296181</v>
       </c>
       <c r="H11" s="12" t="e">
         <f>Bond_Allocation!#REF!/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2484,7 +2519,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A12" t="str">
         <f>Price_Data!B12</f>
         <v>금</v>
@@ -2498,15 +2533,15 @@
       </c>
       <c r="D12" s="16">
         <f>Price_Data!C12</f>
-        <v>4255.1000000000004</v>
+        <v>4332.01</v>
       </c>
       <c r="E12" s="13">
         <f t="shared" si="0"/>
-        <v>127653.00000000001</v>
+        <v>129960.3</v>
       </c>
       <c r="F12" s="12">
         <f t="shared" si="1"/>
-        <v>3.9224457443093767E-2</v>
+        <v>4.0070613656166806E-2</v>
       </c>
       <c r="H12" s="12" t="e">
         <f>Satellite_Selection!F10/SUM(Core_Allocation!D10,Core_Allocation!D11,Core_Allocation!D12,Core_Allocation!#REF!,Bond_Allocation!D8,Bond_Allocation!#REF!,Satellite_Selection!F10,Satellite_Selection!F11,Satellite_Selection!F12)</f>
@@ -2514,24 +2549,24 @@
       </c>
       <c r="I12" s="13">
         <f>Satellite_Selection!F10</f>
-        <v>1278720</v>
+        <v>1260000</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="2"/>
-        <v>1151067</v>
+        <v>1130039.7</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="3"/>
-        <v>매수 ₩1,151,067</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>매수 ₩1,130,040</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A13" s="7" t="s">
         <v>51</v>
       </c>
       <c r="E13" s="14">
         <f>SUM(E6:E12)</f>
-        <v>3254423.6</v>
+        <v>3243282</v>
       </c>
       <c r="F13" s="17">
         <f>SUM(F6:F12)</f>
@@ -2542,12 +2577,12 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A16" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A17" s="1" t="s">
         <v>75</v>
       </c>
@@ -2574,19 +2609,19 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="20.65" x14ac:dyDescent="0.7">
       <c r="A1" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
@@ -2609,7 +2644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -2632,21 +2667,21 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>89</v>
       </c>
       <c r="B5" s="13">
         <f>Rebalancing!E13</f>
-        <v>3254423.6</v>
+        <v>3243282</v>
       </c>
       <c r="C5" s="12">
         <f>(B5-B4)/B4</f>
-        <v>-0.89151921333333328</v>
+        <v>-0.89189059999999998</v>
       </c>
       <c r="D5" s="12">
         <f>(B5-B$4)/B$4</f>
-        <v>-0.89151921333333328</v>
+        <v>-0.89189059999999998</v>
       </c>
       <c r="E5" s="12">
         <f>Asset_Allocation!B4/100</f>
@@ -2667,21 +2702,21 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="24.75" x14ac:dyDescent="0.85">
       <c r="A1" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>91</v>
       </c>
@@ -2690,57 +2725,57 @@
         <v>45965</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="19.149999999999999" x14ac:dyDescent="0.7">
       <c r="A4" s="19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="20">
         <f>Rebalancing!E13</f>
-        <v>3254423.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3243282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6" s="12">
         <f>Performance!C5</f>
-        <v>-0.89151921333333328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-0.89189059999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7" s="12">
         <f>Performance!D5</f>
-        <v>-0.89151921333333328</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+        <v>-0.89189059999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="19.149999999999999" x14ac:dyDescent="0.7">
       <c r="A9" s="19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="21">
         <f>SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"S&amp;P500")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"KOSPI")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"CSI300")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Europe")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Apple")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Tesla")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Exxon")</f>
-        <v>66443.100000000006</v>
+        <v>68651.7</v>
       </c>
       <c r="C10" s="12">
         <f>B10/B5</f>
-        <v>2.0416242065107938E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.1167354550113125E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>97</v>
       </c>
@@ -2753,20 +2788,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="21">
         <f>SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"S&amp;P500")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"KOSPI")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"CSI300")+SUMIFS(Rebalancing!E:E,Rebalancing!A:A,"Europe")</f>
-        <v>66443.100000000006</v>
+        <v>68651.7</v>
       </c>
       <c r="C13" s="12">
         <f>B13/B5</f>
-        <v>2.0416242065107938E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2.1167354550113125E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>99</v>
       </c>
@@ -2779,12 +2814,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="19.149999999999999" x14ac:dyDescent="0.7">
       <c r="A16" s="19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A17" s="1" t="s">
         <v>101</v>
       </c>
@@ -2798,75 +2833,75 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A18" t="str">
         <f>Rebalancing!A6</f>
         <v>S&amp;P500</v>
       </c>
       <c r="B18" s="13">
         <f>Rebalancing!E6</f>
-        <v>66443.100000000006</v>
+        <v>68651.7</v>
       </c>
       <c r="C18" s="12">
         <f>Rebalancing!F6</f>
-        <v>2.0416242065107938E-2</v>
+        <v>2.1167354550113125E-2</v>
       </c>
       <c r="D18" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A19" t="str">
         <f>Rebalancing!A7</f>
         <v>KOSPI200</v>
       </c>
       <c r="B19" s="13">
         <f>Rebalancing!E7</f>
-        <v>193900</v>
+        <v>218400</v>
       </c>
       <c r="C19" s="12">
         <f>Rebalancing!F7</f>
-        <v>5.9580443062175435E-2</v>
+        <v>6.7339195296616208E-2</v>
       </c>
       <c r="D19" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A20" t="str">
         <f>Rebalancing!A8</f>
         <v>TIGER 차이나테크 TOP10</v>
       </c>
       <c r="B20" s="13">
         <f>Rebalancing!E8</f>
-        <v>1277000</v>
+        <v>1237000</v>
       </c>
       <c r="C20" s="12">
         <f>Rebalancing!F8</f>
-        <v>0.39238899324599291</v>
+        <v>0.38140377555821542</v>
       </c>
       <c r="D20" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A21" t="str">
         <f>Rebalancing!A9</f>
         <v>미국채 20년</v>
       </c>
       <c r="B21" s="13">
         <f>Rebalancing!E9</f>
-        <v>4510.5</v>
+        <v>4353</v>
       </c>
       <c r="C21" s="12">
         <f>Rebalancing!F9</f>
-        <v>1.3859597134189907E-3</v>
+        <v>1.3421589612004137E-3</v>
       </c>
       <c r="D21" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A22" t="str">
         <f>Rebalancing!A10</f>
         <v>Frontline Plc</v>
@@ -2877,13 +2912,13 @@
       </c>
       <c r="C22" s="12">
         <f>Rebalancing!F10</f>
-        <v>0.23955240491741764</v>
+        <v>0.24037533584806994</v>
       </c>
       <c r="D22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A23" t="str">
         <f>Rebalancing!A11</f>
         <v>Antero Resources Corp</v>
@@ -2894,24 +2929,24 @@
       </c>
       <c r="C23" s="12">
         <f>Rebalancing!F11</f>
-        <v>0.2474514995527933</v>
+        <v>0.2483015661296181</v>
       </c>
       <c r="D23" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A24" t="str">
         <f>Rebalancing!A12</f>
         <v>금</v>
       </c>
       <c r="B24" s="13">
         <f>Rebalancing!E12</f>
-        <v>127653.00000000001</v>
+        <v>129960.3</v>
       </c>
       <c r="C24" s="12">
         <f>Rebalancing!F12</f>
-        <v>3.9224457443093767E-2</v>
+        <v>4.0070613656166806E-2</v>
       </c>
       <c r="D24" t="s">
         <v>86</v>

--- a/Portfolio/Portfolio_Rebalancing_Template.xlsx
+++ b/Portfolio/Portfolio_Rebalancing_Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29630"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://goe0200-my.sharepoint.com/personal/wngml0630_kwangsunge_goe_go_kr/Documents/macro_strategy/Portfolio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KoreaPDS\Work\macro_strategy\Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="11_8C0B8BEF93006CC2432FAC54C2245937AAE96A49" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22F057F7-FF11-4715-A586-0AE9EAC6E509}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="21795" windowHeight="12975" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Price_Data" sheetId="1" r:id="rId1"/>
@@ -43,7 +42,7 @@
     <definedName name="TreeMap">"TreeMap"</definedName>
     <definedName name="Waterfall">"Waterfall"</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -458,7 +457,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0.0&quot;%&quot;"/>
     <numFmt numFmtId="177" formatCode="0.0000"/>
@@ -883,16 +882,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
     <col min="3" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -921,7 +920,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -953,7 +952,7 @@
         <v>16.982389176201956</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>114</v>
       </c>
@@ -985,7 +984,7 @@
         <v>96.226415094339629</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>122</v>
       </c>
@@ -1017,7 +1016,7 @@
         <v>22.016176760702308</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1049,7 +1048,7 @@
         <v>-6.6580894178192285</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
@@ -1057,7 +1056,7 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>104</v>
       </c>
@@ -1089,7 +1088,7 @@
         <v>32.113037893384714</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -1121,7 +1120,7 @@
         <v>4.6803303762618578</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>111</v>
       </c>
@@ -1153,7 +1152,7 @@
         <v>66.912092815707283</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -1185,7 +1184,7 @@
         <v>27.696078431372545</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>125</v>
       </c>
@@ -1217,7 +1216,7 @@
         <v>-22.129032258064516</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -1256,26 +1255,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.75" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="14" customWidth="1"/>
     <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.65" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:11" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -1301,7 +1300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1326,7 +1325,7 @@
         <v>39.480644849611487</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1351,7 +1350,7 @@
         <v>60.51935515038852</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>Price_Data!B4</f>
         <v>TIGER 차이나테크 TOP10</v>
@@ -1376,17 +1375,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D8" s="3"/>
       <c r="E8" s="9"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -1412,7 +1411,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1437,12 +1436,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -1456,7 +1455,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>Price_Data!B7</f>
         <v>Frontline Plc</v>
@@ -1474,7 +1473,7 @@
         <v>🔴 제외</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>Price_Data!B8</f>
         <v>Antero Resources Corp</v>
@@ -1492,7 +1491,7 @@
         <v>🟢 보유</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>Price_Data!B12</f>
         <v>금</v>
@@ -1510,7 +1509,7 @@
         <v>🟢 보유</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>Price_Data!B9</f>
         <v>희토류</v>
@@ -1528,7 +1527,7 @@
         <v>🟢 보유</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>Price_Data!B10</f>
         <v>구리</v>
@@ -1546,7 +1545,7 @@
         <v>🟢 보유</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>Price_Data!B11</f>
         <v>Sportt Uranium Miners ETF</v>
@@ -1571,26 +1570,26 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.65" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:3" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>116</v>
       </c>
@@ -1601,7 +1600,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1613,12 +1612,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1626,7 +1625,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -1634,7 +1633,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1642,13 +1641,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.6"/>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1659,7 +1658,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1671,13 +1670,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B18" s="11"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B19" s="11"/>
     </row>
   </sheetData>
@@ -1687,21 +1686,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.65" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>12600000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>117</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>10080000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>5040000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>Price_Data!B2</f>
         <v>S&amp;P500</v>
@@ -1785,14 +1785,14 @@
         <v>SPY</v>
       </c>
       <c r="F10">
-        <v>709180</v>
+        <v>1046610</v>
       </c>
       <c r="G10" s="13">
         <f>D10-F10</f>
-        <v>1280644.5004204188</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.6">
+        <v>943214.5004204188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>Price_Data!B3</f>
         <v>KOSPI200</v>
@@ -1814,14 +1814,14 @@
         <v>K51</v>
       </c>
       <c r="F11">
-        <v>1330000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="13">
         <f>D11-F11</f>
-        <v>1720175.4995795814</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.6">
+        <v>3050175.4995795814</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>Price_Data!B4</f>
         <v>TIGER 차이나테크 TOP10</v>
@@ -1843,14 +1843,14 @@
         <v>0047A0</v>
       </c>
       <c r="F12">
-        <v>549610</v>
+        <v>0</v>
       </c>
       <c r="G12" s="13">
         <f>D12-F12</f>
-        <v>-549610</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>51</v>
       </c>
@@ -1862,29 +1862,34 @@
         <f>SUM(D10:D12)</f>
         <v>5040000</v>
       </c>
+      <c r="G13" s="13">
+        <f>G12+G11+G10</f>
+        <v>3993390</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.65" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1893,7 +1898,7 @@
         <v>12600000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -1902,7 +1907,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -1911,7 +1916,7 @@
         <v>2520000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>55</v>
       </c>
@@ -1928,7 +1933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1948,14 +1953,14 @@
         <v>12</v>
       </c>
       <c r="F8">
-        <v>1324670</v>
+        <v>1870305</v>
       </c>
       <c r="G8" s="13">
         <f>D8-F8</f>
-        <v>1195330</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.6">
+        <v>649695</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>51</v>
       </c>
@@ -1975,21 +1980,21 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20.65" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1998,7 +2003,7 @@
         <v>12600000</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -2007,7 +2012,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -2016,7 +2021,7 @@
         <v>10080000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -2025,7 +2030,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -2034,7 +2039,7 @@
         <v>5040000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>59</v>
       </c>
@@ -2057,7 +2062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>Price_Data!B7</f>
         <v>Frontline Plc</v>
@@ -2085,14 +2090,14 @@
         <v>FRO</v>
       </c>
       <c r="H10">
-        <v>912648</v>
+        <v>1227833</v>
       </c>
       <c r="I10" s="13">
         <f>F10-H10</f>
-        <v>347352</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
+        <v>32167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>Price_Data!B8</f>
         <v>Antero Resources Corp</v>
@@ -2120,14 +2125,14 @@
         <v>AR</v>
       </c>
       <c r="H11">
-        <v>1006348</v>
+        <v>1120706</v>
       </c>
       <c r="I11" s="13">
         <f>F11-H11</f>
-        <v>253652</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
+        <v>139294</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>Price_Data!B12</f>
         <v>금</v>
@@ -2155,14 +2160,14 @@
         <v>GC1</v>
       </c>
       <c r="H12">
-        <v>939080</v>
+        <v>1320660</v>
       </c>
       <c r="I12" s="13">
         <f>F12-H12</f>
-        <v>1076920</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
+        <v>695340</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>Price_Data!B11</f>
         <v>Sportt Uranium Miners ETF</v>
@@ -2191,7 +2196,7 @@
       </c>
       <c r="I13" s="13"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>51</v>
       </c>
@@ -2202,6 +2207,10 @@
       <c r="F14" s="14">
         <f>SUM(F10:F12)</f>
         <v>4536000</v>
+      </c>
+      <c r="I14" s="13">
+        <f>I13+I12+I11+I10</f>
+        <v>866801</v>
       </c>
     </row>
   </sheetData>
@@ -2212,9 +2221,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
@@ -2224,12 +2233,12 @@
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.65" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:11" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -2237,12 +2246,12 @@
         <v>45965</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -2275,7 +2284,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>Price_Data!B2</f>
         <v>S&amp;P500</v>
@@ -2316,7 +2325,7 @@
         <v>매수 ₩1,921,173</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>Price_Data!B3</f>
         <v>KOSPI200</v>
@@ -2357,7 +2366,7 @@
         <v>매수 ₩2,831,775</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>Price_Data!B4</f>
         <v>TIGER 차이나테크 TOP10</v>
@@ -2398,7 +2407,7 @@
         <v>매도 ₩1,237,000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>Price_Data!B5</f>
         <v>미국채 20년</v>
@@ -2439,7 +2448,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>Price_Data!B7</f>
         <v>Frontline Plc</v>
@@ -2479,7 +2488,7 @@
         <v>매수 ₩1,740,395</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>Price_Data!B8</f>
         <v>Antero Resources Corp</v>
@@ -2519,7 +2528,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>Price_Data!B12</f>
         <v>금</v>
@@ -2560,7 +2569,7 @@
         <v>매수 ₩1,130,040</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>51</v>
       </c>
@@ -2577,12 +2586,12 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>75</v>
       </c>
@@ -2609,19 +2618,19 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.65" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
@@ -2644,7 +2653,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -2667,7 +2676,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>89</v>
       </c>
@@ -2702,21 +2711,21 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24.75" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.5">
       <c r="A1" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>91</v>
       </c>
@@ -2725,12 +2734,12 @@
         <v>45965</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -2739,7 +2748,7 @@
         <v>3243282</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>93</v>
       </c>
@@ -2748,7 +2757,7 @@
         <v>-0.89189059999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>94</v>
       </c>
@@ -2757,12 +2766,12 @@
         <v>-0.89189059999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>96</v>
       </c>
@@ -2775,7 +2784,7 @@
         <v>2.1167354550113125E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>97</v>
       </c>
@@ -2788,7 +2797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>98</v>
       </c>
@@ -2801,7 +2810,7 @@
         <v>2.1167354550113125E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>99</v>
       </c>
@@ -2814,12 +2823,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="19.149999999999999" x14ac:dyDescent="0.7">
+    <row r="16" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>101</v>
       </c>
@@ -2833,7 +2842,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>Rebalancing!A6</f>
         <v>S&amp;P500</v>
@@ -2850,7 +2859,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>Rebalancing!A7</f>
         <v>KOSPI200</v>
@@ -2867,7 +2876,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>Rebalancing!A8</f>
         <v>TIGER 차이나테크 TOP10</v>
@@ -2884,7 +2893,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>Rebalancing!A9</f>
         <v>미국채 20년</v>
@@ -2901,7 +2910,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>Rebalancing!A10</f>
         <v>Frontline Plc</v>
@@ -2918,7 +2927,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>Rebalancing!A11</f>
         <v>Antero Resources Corp</v>
@@ -2935,7 +2944,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>Rebalancing!A12</f>
         <v>금</v>
